--- a/MinMax/scripts/comparison/accuracy_comparison_table_57_25_False.xlsx
+++ b/MinMax/scripts/comparison/accuracy_comparison_table_57_25_False.xlsx
@@ -31,88 +31,88 @@
     <t>Metric [MSE]</t>
   </si>
   <si>
+    <t>qg_tot</t>
+  </si>
+  <si>
+    <t>vi_tot</t>
+  </si>
+  <si>
+    <t>pg_tot</t>
+  </si>
+  <si>
+    <t>Iinj_r_tot</t>
+  </si>
+  <si>
+    <t>Ibr_to_i_tot</t>
+  </si>
+  <si>
+    <t>cost_tot</t>
+  </si>
+  <si>
+    <t>Ibr_to_r_tot</t>
+  </si>
+  <si>
+    <t>solve_time</t>
+  </si>
+  <si>
+    <t>qinj_tot</t>
+  </si>
+  <si>
+    <t>Ibr_from_r_tot</t>
+  </si>
+  <si>
+    <t>qd_tot</t>
+  </si>
+  <si>
+    <t>vm_tot</t>
+  </si>
+  <si>
+    <t>vr_tot</t>
+  </si>
+  <si>
+    <t>Ibr_from_i_tot</t>
+  </si>
+  <si>
     <t>Iinj_i_tot</t>
   </si>
   <si>
-    <t>qinj_tot</t>
+    <t>pd_tot</t>
+  </si>
+  <si>
+    <t>slack_tot</t>
   </si>
   <si>
     <t>pinj_tot</t>
   </si>
   <si>
-    <t>Ibr_from_i_tot</t>
-  </si>
-  <si>
-    <t>solve_time</t>
-  </si>
-  <si>
-    <t>vm_tot</t>
-  </si>
-  <si>
-    <t>vi_tot</t>
-  </si>
-  <si>
-    <t>cost_tot</t>
-  </si>
-  <si>
-    <t>Ibr_to_r_tot</t>
-  </si>
-  <si>
-    <t>slack_tot</t>
-  </si>
-  <si>
-    <t>qd_tot</t>
-  </si>
-  <si>
-    <t>vr_tot</t>
-  </si>
-  <si>
-    <t>Ibr_from_r_tot</t>
-  </si>
-  <si>
-    <t>pd_tot</t>
-  </si>
-  <si>
-    <t>Iinj_r_tot</t>
-  </si>
-  <si>
-    <t>pg_tot</t>
-  </si>
-  <si>
-    <t>qg_tot</t>
-  </si>
-  <si>
-    <t>Ibr_to_i_tot</t>
-  </si>
-  <si>
-    <t>0.41s (0.30 s)</t>
-  </si>
-  <si>
     <t>29849.18 (26155.34 &gt; 14.58%)</t>
   </si>
   <si>
+    <t>0.66s (0.91 s)</t>
+  </si>
+  <si>
     <t>1.73 (2.45)</t>
   </si>
   <si>
-    <t>0.15s (0.30 s)</t>
-  </si>
-  <si>
     <t>26352.22 (26155.34 &gt; 0.76%)</t>
   </si>
   <si>
+    <t>0.40s (0.91 s)</t>
+  </si>
+  <si>
     <t>2.35 (2.45)</t>
   </si>
   <si>
-    <t>0.34s (0.30 s)</t>
-  </si>
-  <si>
     <t>26158.49 (26155.34 &gt; 0.01%)</t>
   </si>
   <si>
+    <t>0.92s (0.91 s)</t>
+  </si>
+  <si>
     <t>2.45 (2.45)</t>
   </si>
   <si>
-    <t>0.32s (0.30 s)</t>
+    <t>0.73s (0.91 s)</t>
   </si>
 </sst>
 </file>
@@ -495,16 +495,16 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>0.01245012879371643</v>
+        <v>0.1513532251119614</v>
       </c>
       <c r="C2">
-        <v>0.002801903057843447</v>
+        <v>0.02467119321227074</v>
       </c>
       <c r="D2">
-        <v>0.0009892971720546484</v>
+        <v>0.006161452736705542</v>
       </c>
       <c r="E2">
-        <v>0.0009892971720546484</v>
+        <v>0.006161452736705542</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -512,16 +512,16 @@
         <v>6</v>
       </c>
       <c r="B3">
-        <v>0.01634609699249268</v>
+        <v>0.009907729923725128</v>
       </c>
       <c r="C3">
-        <v>0.003046463709324598</v>
+        <v>2.215746644651517E-05</v>
       </c>
       <c r="D3">
-        <v>0.000991008011624217</v>
+        <v>6.635672889387934E-06</v>
       </c>
       <c r="E3">
-        <v>0.000991008011624217</v>
+        <v>6.635672889387934E-06</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -529,16 +529,16 @@
         <v>7</v>
       </c>
       <c r="B4">
-        <v>0.9429539442062378</v>
+        <v>8.847691535949707</v>
       </c>
       <c r="C4">
-        <v>0.001873748376965523</v>
+        <v>0.0158852394670248</v>
       </c>
       <c r="D4">
-        <v>4.10439815823338E-06</v>
+        <v>3.899205330526456E-05</v>
       </c>
       <c r="E4">
-        <v>4.10439815823338E-06</v>
+        <v>3.899205330526456E-05</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -546,50 +546,50 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>0.006206559482961893</v>
+        <v>0.9366517663002014</v>
       </c>
       <c r="C5">
-        <v>0.0008503496646881104</v>
+        <v>0.002014635130763054</v>
       </c>
       <c r="D5">
-        <v>0.000506330921780318</v>
+        <v>9.732608305057511E-06</v>
       </c>
       <c r="E5">
-        <v>0.000506330921780318</v>
+        <v>9.732608305057511E-06</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" t="s">
-        <v>29</v>
-      </c>
-      <c r="E6" t="s">
-        <v>32</v>
+      <c r="B6">
+        <v>0.00616479991003871</v>
+      </c>
+      <c r="C6">
+        <v>0.0008423297549597919</v>
+      </c>
+      <c r="D6">
+        <v>0.000498531386256218</v>
+      </c>
+      <c r="E6">
+        <v>0.000498531386256218</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B7">
-        <v>0.0008681614999659359</v>
-      </c>
-      <c r="C7">
-        <v>0.0001225811283802614</v>
-      </c>
-      <c r="D7">
-        <v>0.0001149207237176597</v>
-      </c>
-      <c r="E7">
-        <v>0.0001149207237176597</v>
+      <c r="B7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -597,16 +597,16 @@
         <v>11</v>
       </c>
       <c r="B8">
-        <v>0.009907729923725128</v>
+        <v>0.354483038187027</v>
       </c>
       <c r="C8">
-        <v>2.215747190348338E-05</v>
+        <v>0.0006735518109053373</v>
       </c>
       <c r="D8">
-        <v>6.635672889387934E-06</v>
+        <v>6.835913154645823E-06</v>
       </c>
       <c r="E8">
-        <v>6.635672889387934E-06</v>
+        <v>6.835913154645823E-06</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -623,7 +623,7 @@
         <v>30</v>
       </c>
       <c r="E9" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -631,33 +631,33 @@
         <v>13</v>
       </c>
       <c r="B10">
-        <v>0.354483038187027</v>
+        <v>0.01634609699249268</v>
       </c>
       <c r="C10">
-        <v>0.0006735522765666246</v>
+        <v>0.003046464174985886</v>
       </c>
       <c r="D10">
-        <v>6.835913154645823E-06</v>
+        <v>0.000991008011624217</v>
       </c>
       <c r="E10">
-        <v>6.835913154645823E-06</v>
+        <v>0.000991008011624217</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B11" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" t="s">
-        <v>28</v>
-      </c>
-      <c r="D11" t="s">
-        <v>31</v>
-      </c>
-      <c r="E11" t="s">
-        <v>31</v>
+      <c r="B11">
+        <v>0.3537828922271729</v>
+      </c>
+      <c r="C11">
+        <v>0.0006728973821736872</v>
+      </c>
+      <c r="D11">
+        <v>6.853253125882475E-06</v>
+      </c>
+      <c r="E11">
+        <v>6.853253125882475E-06</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -682,16 +682,16 @@
         <v>16</v>
       </c>
       <c r="B13">
-        <v>0.001133074285462499</v>
+        <v>0.0008681614999659359</v>
       </c>
       <c r="C13">
-        <v>0.0001199237303808331</v>
+        <v>0.0001225811283802614</v>
       </c>
       <c r="D13">
-        <v>0.0001128071671701036</v>
+        <v>0.0001149207237176597</v>
       </c>
       <c r="E13">
-        <v>0.0001128071671701036</v>
+        <v>0.0001149207237176597</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -699,16 +699,16 @@
         <v>17</v>
       </c>
       <c r="B14">
-        <v>0.3537828922271729</v>
+        <v>0.001133074285462499</v>
       </c>
       <c r="C14">
-        <v>0.0006728980224579573</v>
+        <v>0.0001199237303808331</v>
       </c>
       <c r="D14">
-        <v>6.853253125882475E-06</v>
+        <v>0.0001128071671701036</v>
       </c>
       <c r="E14">
-        <v>6.853253125882475E-06</v>
+        <v>0.0001128071671701036</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -716,16 +716,16 @@
         <v>18</v>
       </c>
       <c r="B15">
-        <v>3.130812444064206E-16</v>
+        <v>0.006206559482961893</v>
       </c>
       <c r="C15">
-        <v>3.130812444064206E-16</v>
+        <v>0.0008503497228957713</v>
       </c>
       <c r="D15">
-        <v>3.130812444064206E-16</v>
+        <v>0.000506330921780318</v>
       </c>
       <c r="E15">
-        <v>3.130812444064206E-16</v>
+        <v>0.000506330921780318</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -733,16 +733,16 @@
         <v>19</v>
       </c>
       <c r="B16">
-        <v>0.9366517663002014</v>
+        <v>0.01245012879371643</v>
       </c>
       <c r="C16">
-        <v>0.002014636760577559</v>
+        <v>0.002801903756335378</v>
       </c>
       <c r="D16">
-        <v>9.732608305057511E-06</v>
+        <v>0.0009892971720546484</v>
       </c>
       <c r="E16">
-        <v>9.732608305057511E-06</v>
+        <v>0.0009892971720546484</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -750,33 +750,33 @@
         <v>20</v>
       </c>
       <c r="B17">
-        <v>8.847691535949707</v>
+        <v>3.130812444064206E-16</v>
       </c>
       <c r="C17">
-        <v>0.0158852506428957</v>
+        <v>3.130812444064206E-16</v>
       </c>
       <c r="D17">
-        <v>3.899205330526456E-05</v>
+        <v>3.130812444064206E-16</v>
       </c>
       <c r="E17">
-        <v>3.899205330526456E-05</v>
+        <v>3.130812444064206E-16</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B18">
-        <v>0.1513532251119614</v>
-      </c>
-      <c r="C18">
-        <v>0.02467118948698044</v>
-      </c>
-      <c r="D18">
-        <v>0.006161452736705542</v>
-      </c>
-      <c r="E18">
-        <v>0.006161452736705542</v>
+      <c r="B18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" t="s">
+        <v>28</v>
+      </c>
+      <c r="D18" t="s">
+        <v>31</v>
+      </c>
+      <c r="E18" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -784,16 +784,16 @@
         <v>22</v>
       </c>
       <c r="B19">
-        <v>0.00616479991003871</v>
+        <v>0.9429539442062378</v>
       </c>
       <c r="C19">
-        <v>0.0008423297549597919</v>
+        <v>0.001873746863566339</v>
       </c>
       <c r="D19">
-        <v>0.000498531386256218</v>
+        <v>4.10439815823338E-06</v>
       </c>
       <c r="E19">
-        <v>0.000498531386256218</v>
+        <v>4.10439815823338E-06</v>
       </c>
     </row>
   </sheetData>
